--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/region-de-coquimbo.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/region-de-coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3714-218-CM26</t>
+          <t>1232565-6-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>MUEBLES ANDROMEDA DOS SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.285.439-0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,43 +569,43 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>15549.88</v>
+        <v>41541.52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2288-667-CM26</t>
+          <t>2450-147-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,43 +630,43 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>90497.82000000001</v>
+        <v>12935.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1232565-213-CM26</t>
+          <t>627786-28-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,28 +691,28 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6400.97</v>
+        <v>7249.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1232565-216-CM26</t>
+          <t>1004823-26-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.999.280-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,33 +752,33 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7106.25</v>
+        <v>8238.969999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5416-802-CM26</t>
+          <t>1232565-55-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,28 +813,28 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9177.83</v>
+        <v>8752.92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2145-711-CM26</t>
+          <t>1698-170-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,6 +874,799 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
+        <v>5858.47</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1698-202-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>OFISILLAS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.855.435-8</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>7018.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1232565-185-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>40144.87</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2448-694-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>23811.37</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1232565-283-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>6729</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4295-33-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.040.100-2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>49737.77</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2450-761-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.040.100-2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>18014.09</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3276-33-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>8774.059999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3714-218-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>15549.88</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2288-667-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.041.300-0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CANELA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>90497.82000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1232565-213-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>6400.97</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1232565-216-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>7106.25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5416-802-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>9177.83</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2145-711-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>61.606.409-6</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>92.999.000-5</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
         <v>15895.55</v>
       </c>
     </row>
